--- a/docs/KRA-library-correction-log-25Sep2026.xlsx
+++ b/docs/KRA-library-correction-log-25Sep2026.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Sets corrected" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Shelves added" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Rows cleaned" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Employee master" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 All shelves" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Departments corrected" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Shelves that moved" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Sets corrected" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Shelves added" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Rows cleaned" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Still open" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 All shelves" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,147 +456,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>What changed in this file</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>What changed, and in what order to upload it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rebuilt from the 2,217-row library published on 25 Sep 2026 plus the live employee master. No KRA text was rewritten: every row still comes from a set Mindgate supplied.</t>
+          <t>Two files. Upload the employee file first, then clear the library and upload the library file — an upload only replaces the shelves present in it, so retired shelves would otherwise stay behind.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>File</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>What it means</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>What it does</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Shelves in the corrected file</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>227</v>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>employee-department-corrections-25Sep2026.xlsx</t>
+        </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>One per designation + department pair that at least one active employee holds</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Moves nine employees to the department their work actually sits in. Only the Department column changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>KRA rows</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>2315</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>KRA Library screen &gt; Clear</t>
+        </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Was 2,217 across 211 shelves</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Empties the library. Needs a typed confirmation. KRAs already on somebody’s sheet are untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Shelves whose KRA set was corrected</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>8</v>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>KRA-library-upload-corrected-25Sep2026.xlsx</t>
+        </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>They carried a set written for a different job — tab 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Shelves added</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Nobody in these departments had a shelf of their own — tab 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Shelves removed</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Vice President [Tester] — no active employee holds that title in that department</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Rows cleaned</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Numbering prefixes, "| Source:" tails, one spreadsheet total, one lost title — tab 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Shelves whose weights total 100</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>227</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Checked after cleaning; none drifted</t>
+          <t>225 shelves, 2295 KRAs. Every shelf reaches at least one employee and totals 100.</t>
         </is>
       </c>
     </row>
@@ -613,7 +561,566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nine employees moved, eight shelves with them</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The rule applied: the department must match the work the KRAs describe. Application Support Executive (L2) was the one you flagged; the other seven follow the same test. Where the department the person moves into already publishes a shelf for that title, they simply join it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Employee code</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Department was</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Department now</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MGSD1126</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Amila  Upendra</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MGS5431</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Aniket Sadar</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Recon Executive</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MGS1613</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Harshad Murumkar</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Software Tester</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MGS1902</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Kalpesh Rasal</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Recon Executive</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>MGSD1110</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Mohan  M B</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager – Implementation</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MGS1966</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Pankaj Chikte</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Application Support Executive (L2)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Application Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MGS2178</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ranjan Mohapatra</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>IT Operation Manager</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>MGS1836</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Shweta Nair</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Executive Operations (Merchant OnBoarding)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MGSD1123</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Swastika  Nayak</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The library follows the people</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Development no longer lists Application Support Executive (L2); Support no longer lists a recon or merchant role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Department now</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>KRAs</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>What happened</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Application Support Executive (L2)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Application Support</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Development: the department contradicted the work these KRAs describe. carried the Customer Support Executive set (helpdesk tickets, FCR, CSAT). An L2 application support engineer does defect analysis and incident work, so it now carries the L2 Support set.  (13 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Development: the department contradicted the work these KRAs describe.  (7 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Executive Operations (Merchant OnBoarding)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Support: the department contradicted the work these KRAs describe. carried the 33-KRA L1 Support set. The role is merchant onboarding, so it now carries the merchant onboarding set.  (16 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>IT Operation Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Development: the department contradicted the work these KRAs describe. carried the software Technical Manager set (code review, architecture, project budget). Now carries the IT &amp; Security manager set.  (10 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Recon Executive</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>moved out of INFRA and joined the shelf already published there: the department contradicted the work these KRAs describe.  (11 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Software Tester</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Development and joined the shelf already published there: the department contradicted the work these KRAs describe.  (12 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Sr Manager – Implementation</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Development: the department contradicted the work these KRAs describe.  (7 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Recon Executive</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>moved out of Support: the department contradicted the work these KRAs describe.  (11 KRAs)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -626,14 +1133,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Eight shelves carried a KRA set written for a different job</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>Shelves that carried a KRA set written for a different job</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each now carries the set that matches its designation. The Comments column of those rows is tagged "[Set corrected 25-Sep-2026]" so you can find them in the app.</t>
+          <t>Each now carries the set matching its designation. Rows tagged "[Set corrected 25-Sep-2026]" in Comments.</t>
         </is>
       </c>
     </row>
@@ -655,7 +1162,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>KRAs now</t>
+          <t>KRAs</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -664,33 +1171,33 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Application Support Executive (L2)</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>carried the Customer Support Executive set (helpdesk tickets, FCR, CSAT). An L2 application support engineer does defect analysis and incident work, so it now carries the L2 Support set.  (13 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
+          <t>carried the IT Operations Executive set (ticket logging, systems inventory). Now carries the business analyst set.  (6 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Consultant - DevOps</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -702,18 +1209,18 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>carried the IT Operations Executive set (ticket logging, systems inventory). Now carries the business analyst set.  (6 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
+          <t>carried the Cloud Operations Engineer set (support tickets, inventory). Now carries the DevOps engineer set.  (7 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Consultant - DevOps</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -729,120 +1236,28 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>carried the Cloud Operations Engineer set (support tickets, inventory). Now carries the DevOps engineer set.  (7 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
+          <t>carried the Cloud Operations Engineer set. Now carries the senior developer set.  (7 KRAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Executive Operations (Merchant OnBoarding)</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>carried the 33-KRA L1 Support set. The role is merchant onboarding, so it now carries the merchant onboarding set.  (16 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>IT Operation Manager</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>carried the software Technical Manager set (code review, architecture, project budget). Now carries the IT &amp; Security manager set.  (10 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>carried the Cloud Operations Engineer set. Now carries the senior developer set.  (7 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Software Tester</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>carried the Software Analyst set (FSD/SRS authoring, use-case mapping). A tester now carries the tester set.  (12 KRAs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>System Administrator</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>carried the Office Assistant set (mail dispatch, pantry, office hygiene, petty cash). Now carries the system administration set.  (10 KRAs)</t>
         </is>
@@ -857,7 +1272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -880,10 +1295,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Five departments had no shelf of any kind: Sales (15 people), TBS (3), Legal &amp; Compliance (3), ENBD (2), Management (2). Nothing was invented — each adopts the closest set Mindgate already supplied, and every row is tagged "[New shelf 25-Sep-2026 — adapted, please review]". These are the rows most worth your review.</t>
+          <t>Five departments had none at all: Sales (15 people), TBS (3), Legal &amp; Compliance (3), ENBD (2), Management (2). Nothing was invented — each adopts the closest set Mindgate already supplied, tagged "[New shelf 25-Sep-2026 — adapted, please review]". These are the rows most worth your review.</t>
         </is>
       </c>
     </row>
@@ -914,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Assistant Vice President</t>
@@ -937,7 +1352,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Assistant Vice President</t>
@@ -960,7 +1375,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Business Analyst</t>
@@ -983,7 +1398,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1">
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Business Head</t>
@@ -1006,7 +1421,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="44" customHeight="1">
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Consultant - TBS</t>
@@ -1029,7 +1444,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -1052,7 +1467,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
+    <row r="11" ht="46" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Senior Executive</t>
@@ -1075,7 +1490,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="44" customHeight="1">
+    <row r="12" ht="46" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Senior Manager</t>
@@ -1098,7 +1513,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Senior Manager</t>
@@ -1121,7 +1536,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
+    <row r="14" ht="46" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Senior Vice President I</t>
@@ -1144,7 +1559,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="46" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Senior Vice President II</t>
@@ -1167,7 +1582,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
+    <row r="16" ht="46" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Software Architect</t>
@@ -1190,7 +1605,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="44" customHeight="1">
+    <row r="17" ht="46" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Trainee Tester</t>
@@ -1213,7 +1628,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="44" customHeight="1">
+    <row r="18" ht="46" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Vice President</t>
@@ -1236,7 +1651,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
+    <row r="19" ht="46" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Vice President I</t>
@@ -1259,7 +1674,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
+    <row r="20" ht="46" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Vice President I</t>
@@ -1282,7 +1697,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="44" customHeight="1">
+    <row r="21" ht="46" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Vice President II</t>
@@ -1314,7 +1729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1335,10 +1750,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Titles only — the KRA text, the KPI text and the weights are untouched except where a row was removed, and that shelf was rescaled back to 100.</t>
+          <t>Titles only. The KRA text, the KPI text and the weights are untouched except where a row was removed, and that shelf was rescaled back to 100.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +2015,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>IT Operation Manager [Development]</t>
+          <t>IT Operation Manager [IT]</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1617,7 +2032,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>IT Operation Manager [Development]</t>
+          <t>IT Operation Manager [IT]</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1634,7 +2049,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>IT Operation Manager [Development]</t>
+          <t>IT Operation Manager [IT]</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1651,7 +2066,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>IT Operation Manager [Development]</t>
+          <t>IT Operation Manager [IT]</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1668,7 +2083,7 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>IT Operation Manager [Development]</t>
+          <t>IT Operation Manager [IT]</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1685,7 +2100,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IT Operation Manager [Development]</t>
+          <t>IT Operation Manager [IT]</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2048,32 +2463,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nineteen employee records whose title names a different department</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>Left alone on purpose — two of them need your decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Not fixed here — these are HRMS facts, not library facts. The library follows whatever the master says, so the odd-looking department labels on the KRA Library screen will only disappear once these are corrected on the employee record. Correct them in the HRMS, re-upload the employee master, and we will regenerate this file to match.</t>
+          <t>These are the cases where a title names a department but moving the person would be an organisational decision, not a typo fix. Tell us either way and we will regenerate both files.</t>
         </is>
       </c>
     </row>
@@ -2085,21 +2501,26 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Department on the record</t>
+          <t>Department today</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Department the title names</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Employees</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
+          <t>Our reading</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Needs your decision?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
@@ -2110,16 +2531,21 @@
           <t>IT</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>KRAs are DevOps and a DevOps department exists (18 people). Moving 38 people is a re-org, not a correction.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
@@ -2130,378 +2556,268 @@
           <t>Development</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Same as above.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>Senior Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Same as above.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Consultant - DevOps</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Same as above.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>Senior Software Tester</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Their KRAs are implementation work (install, UAT patch deployment). A tester embedded in an implementation team is a normal structure.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>No — correct as is</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Implementation Officer</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Functional / Delivery / Product is where implementation roles sit in your own sheets.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>No — correct as is</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Implementation Architect</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Same as above.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>No — correct as is</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Software Tester</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Application Support</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Their KRAs are UAT support, which is application-support work.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>No — correct as is</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Trainee Tester</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Application Support</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Same as above.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>No — correct as is</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Senior System Admin</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Implementation Officer</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Trainee Tester</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Application Support</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>"Admin" here means system administration, not the Administration department. We over-flagged this on 25 Sep — it was always correct.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>No — we were wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Electronic Banking Support Executive</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Core Banking Application</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Senior Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Electronic Banking Support Executive</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Core Banking Application</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Customer Support Executive</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Sr. Recon Executive</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Recon</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Sr Manager – Implementation</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Software Tester</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Software Tester</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Application Support</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Recon Executive</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Recon</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Implementation Architect</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>IT Operation Manager</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Executive Operations (Merchant OnBoarding)</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Consultant - DevOps</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Application Support Executive (L2)</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Application Support</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1</v>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Their KRAs are core-banking database support. We over-flagged this on 25 Sep — it was always correct.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>No — we were wrong</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2511,7 +2827,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Designation, department, how many employees it reaches and how many KRAs it carries.</t>
@@ -2576,7 +2892,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -2587,7 +2903,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>set + department corrected</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3432,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>set corrected</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3524,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>set corrected</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3582,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Customer Support</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -3277,7 +3593,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>department corrected</t>
         </is>
       </c>
     </row>
@@ -3703,7 +4019,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -3714,7 +4030,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>set + department corrected</t>
         </is>
       </c>
     </row>
@@ -3841,7 +4157,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -3852,7 +4168,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>set + department corrected</t>
         </is>
       </c>
     </row>
@@ -4807,37 +5123,37 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Recon</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>department corrected</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Recon Executive</t>
+          <t>Security Analyst</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Recon</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
@@ -4853,11 +5169,11 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D105" s="4" t="n">
         <v>8</v>
@@ -4871,7 +5187,7 @@
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Security Analyst</t>
+          <t>Senior Administrator - Network and System</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -4894,19 +5210,19 @@
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Senior Administrator - Network and System</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -4922,11 +5238,11 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D108" s="4" t="n">
         <v>6</v>
@@ -4940,16 +5256,16 @@
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Senior Business Finance Analyst</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Business Finance</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" s="4" t="n">
         <v>6</v>
@@ -4963,19 +5279,19 @@
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Senior Business Finance Analyst</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Business Finance</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
@@ -4986,19 +5302,19 @@
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
@@ -5014,11 +5330,11 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112" s="4" t="n">
         <v>7</v>
@@ -5032,19 +5348,19 @@
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Executive</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
@@ -5060,14 +5376,14 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
@@ -5083,14 +5399,14 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
@@ -5106,14 +5422,14 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
@@ -5129,18 +5445,18 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Legal &amp; Compliance</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
@@ -5152,18 +5468,18 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Legal &amp; Compliance</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5175,14 +5491,14 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Recon</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
@@ -5198,14 +5514,14 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Recon</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
@@ -5216,19 +5532,19 @@
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Senior Executive</t>
+          <t>Senior Graphic Designer</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
@@ -5239,19 +5555,19 @@
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Senior Graphic Designer</t>
+          <t>Senior Linux Administrator</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
@@ -5262,19 +5578,19 @@
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Senior Linux Administrator</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
@@ -5290,14 +5606,14 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Application Support</t>
+          <t>Business Finance</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
@@ -5313,14 +5629,14 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Business Finance</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
@@ -5336,14 +5652,14 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
@@ -5359,14 +5675,14 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
@@ -5382,11 +5698,11 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" s="4" t="n">
         <v>6</v>
@@ -5405,11 +5721,11 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D129" s="4" t="n">
         <v>6</v>
@@ -5428,7 +5744,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
@@ -5451,14 +5767,14 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
@@ -5474,14 +5790,14 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
@@ -5497,14 +5813,14 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
@@ -5520,18 +5836,18 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Legal &amp; Compliance</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
@@ -5543,18 +5859,18 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Legal &amp; Compliance</t>
+          <t>RMG</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5566,18 +5882,18 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>RMG</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
@@ -5589,37 +5905,37 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
@@ -5630,16 +5946,16 @@
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Senior Network Security Engineer</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="n">
         <v>8</v>
@@ -5653,12 +5969,12 @@
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Senior Network Security Engineer</t>
+          <t>Senior OS - Administrator</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
@@ -5676,19 +5992,19 @@
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Senior OS - Administrator</t>
+          <t>Senior Project Manager</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
@@ -5699,19 +6015,19 @@
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Senior Project Manager</t>
+          <t>Senior Security Analyst</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
@@ -5722,7 +6038,7 @@
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Senior Security Analyst</t>
+          <t>Senior SOC Analyst</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -5731,7 +6047,7 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D143" s="4" t="n">
         <v>8</v>
@@ -5745,19 +6061,19 @@
     <row r="144" ht="16" customHeight="1">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Senior SOC Analyst</t>
+          <t>Senior Software Analyst</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
@@ -5773,14 +6089,14 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Application Support</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
@@ -5796,14 +6112,14 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
@@ -5819,14 +6135,14 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
@@ -5842,14 +6158,14 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
@@ -5865,14 +6181,14 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Monitoring Support</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
@@ -5888,14 +6204,14 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Monitoring Support</t>
+          <t>Process Excellence</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
@@ -5911,14 +6227,14 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Process Excellence</t>
+          <t>Production Support</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
@@ -5934,14 +6250,14 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Production Support</t>
+          <t>Recon</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
@@ -5957,14 +6273,14 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Recon</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
@@ -5975,19 +6291,19 @@
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Analyst</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>2</v>
+        <v>227</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
@@ -6003,14 +6319,14 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
@@ -6026,18 +6342,18 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>set corrected</t>
         </is>
       </c>
     </row>
@@ -6049,37 +6365,37 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Tester</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
@@ -6095,14 +6411,14 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
@@ -6113,19 +6429,19 @@
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Tester</t>
+          <t>Senior System Admin</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
@@ -6136,19 +6452,19 @@
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Senior System Admin</t>
+          <t>Senior Technical Lead</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
@@ -6164,14 +6480,14 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
@@ -6182,19 +6498,19 @@
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Senior Technical Lead</t>
+          <t>Senior UI/UX Designer</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
@@ -6205,46 +6521,46 @@
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Senior UI/UX Designer</t>
+          <t>Senior Vice President I</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Senior Vice President I</t>
+          <t>Senior Vice President II</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6256,60 +6572,60 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Senior Vice President II</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C167" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Senior Web Designer</t>
+          <t>Software Analyst</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
@@ -6325,14 +6641,14 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Application Support</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
@@ -6348,14 +6664,14 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
@@ -6371,14 +6687,14 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
@@ -6394,14 +6710,14 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Monitoring Support</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
@@ -6417,14 +6733,14 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Monitoring Support</t>
+          <t>Recon</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
@@ -6440,14 +6756,14 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Recon</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
@@ -6458,53 +6774,53 @@
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Software Analyst</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="C175" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Software Database Developer</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
     <row r="177" ht="16" customHeight="1">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Software Database Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -6513,7 +6829,7 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="D177" s="4" t="n">
         <v>7</v>
@@ -6532,11 +6848,11 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="D178" s="4" t="n">
         <v>7</v>
@@ -6555,14 +6871,14 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Monitoring Support</t>
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
@@ -6578,14 +6894,14 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Monitoring Support</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
@@ -6596,19 +6912,19 @@
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Tester</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
@@ -6624,60 +6940,60 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Application Support</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>department corrected</t>
         </is>
       </c>
     </row>
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Software Tester</t>
+          <t>Sr Manager – Implementation</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>department corrected</t>
         </is>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Software Tester</t>
+          <t>Sr. Business Analyst</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
@@ -6688,19 +7004,19 @@
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Sr Manager – Implementation</t>
+          <t>Sr. Oracle DBA</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
@@ -6711,7 +7027,7 @@
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst</t>
+          <t>Sr. Project Manager</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -6723,7 +7039,7 @@
         <v>1</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
@@ -6734,30 +7050,30 @@
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Sr. Oracle DBA</t>
+          <t>Sr. Recon Executive</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>Recon</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>department corrected</t>
         </is>
       </c>
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>Sr. Project Manager</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6766,10 +7082,10 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
@@ -6780,19 +7096,19 @@
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>Sr. Recon Executive</t>
+          <t>Subject Matter Expert</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
@@ -6803,19 +7119,19 @@
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Support Executive</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
@@ -6826,42 +7142,42 @@
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>Subject Matter Expert</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>set corrected</t>
         </is>
       </c>
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>Support Executive</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
@@ -6872,7 +7188,7 @@
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -6884,30 +7200,30 @@
         <v>1</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>corrected</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
@@ -6923,14 +7239,14 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C195" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
@@ -6941,7 +7257,7 @@
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -6950,10 +7266,10 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
@@ -6964,19 +7280,19 @@
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
@@ -6987,19 +7303,19 @@
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
@@ -7010,19 +7326,19 @@
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Technical Lead</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="D199" s="4" t="n">
-        <v>27</v>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
@@ -7033,19 +7349,19 @@
     <row r="200" ht="16" customHeight="1">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Technical Manager</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C200" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
@@ -7056,19 +7372,19 @@
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Technical Lead</t>
+          <t>Technical Manager</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
@@ -7084,14 +7400,14 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Production Support</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
@@ -7107,11 +7423,11 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Techno functional</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D203" s="4" t="n">
         <v>6</v>
@@ -7125,19 +7441,19 @@
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Technical Manager</t>
+          <t>Tele Caller Assistant</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Production Support</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C204" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
@@ -7148,19 +7464,19 @@
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Technical Manager</t>
+          <t>Trainee</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Techno functional</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
@@ -7171,19 +7487,19 @@
     <row r="206" ht="16" customHeight="1">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Tele Caller Assistant</t>
+          <t>Trainee</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
@@ -7199,14 +7515,14 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Application Support</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
@@ -7222,14 +7538,14 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
@@ -7245,14 +7561,14 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
@@ -7268,14 +7584,14 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
@@ -7291,14 +7607,14 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
@@ -7309,19 +7625,19 @@
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Trainee</t>
+          <t>Trainee Developer</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
@@ -7332,19 +7648,19 @@
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Trainee</t>
+          <t>Trainee Tester</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Application Support</t>
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
@@ -7355,42 +7671,42 @@
     <row r="214" ht="16" customHeight="1">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>Trainee Developer</t>
+          <t>Trainee Tester</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C214" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Trainee Tester</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Application Support</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C215" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
@@ -7401,65 +7717,65 @@
     <row r="216" ht="16" customHeight="1">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Trainee Tester</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Vice President I</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Business Finance</t>
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
@@ -7470,23 +7786,23 @@
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Vice President I</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7498,14 +7814,14 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Business Finance</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
@@ -7521,14 +7837,14 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C221" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
@@ -7544,14 +7860,14 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
@@ -7567,7 +7883,7 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Legal &amp; Compliance</t>
         </is>
       </c>
       <c r="C223" s="4" t="n">
@@ -7578,7 +7894,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7906,7 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C224" s="4" t="n">
@@ -7613,11 +7929,11 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Legal &amp; Compliance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D225" s="4" t="n">
         <v>6</v>
@@ -7631,19 +7947,19 @@
     <row r="226" ht="16" customHeight="1">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>Vice President I</t>
+          <t>Vice President II</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
@@ -7654,23 +7970,23 @@
     <row r="227" ht="16" customHeight="1">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Vice President I</t>
+          <t>Vice President II</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D227" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>added</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7682,85 +7998,39 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>added</t>
         </is>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Vice President II</t>
+          <t>Weblogic Administrator</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="16" customHeight="1">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>Vice President II</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D230" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="16" customHeight="1">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>Weblogic Administrator</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D231" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E231" s="4" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
